--- a/src/test/resources/APR_Report_test.xlsx
+++ b/src/test/resources/APR_Report_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -414,36 +418,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AccountId</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RateType</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RateBasis</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FloorRate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CeilingRate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OverrideCode</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>OverrideRate</t>
         </is>
@@ -460,13 +502,31 @@
           <t>01</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D2" t="n">
-        <v>500</v>
-      </c>
-      <c r="F2" s="1" t="n"/>
+      <c r="H2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.2999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,18 +539,37 @@
           <t>02</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SCRA_AT_CAP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>0.12</v>
       </c>
-      <c r="D3" t="n">
-        <v>300</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>SCRA</t>
         </is>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -505,18 +584,37 @@
           <t>03</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OVERRIDE_HIGHER</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="D4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>CMA</t>
         </is>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -531,19 +629,69 @@
           <t>04</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LOWER</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>CMA</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACC00003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FIXED_ROW</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.2999</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/APR_Report_test.xlsx
+++ b/src/test/resources/APR_Report_test.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,14 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +498,46 @@
           <t>OverrideRate</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ProductCode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OriginationDate</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OverrideExpiry</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProtectionStart</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ProtectionEnd</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>DayCountBasis</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>CompoundingFrequency</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RoundingRule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +575,34 @@
       <c r="I2" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>365</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -572,6 +648,34 @@
       <c r="K3" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>365</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -617,6 +721,34 @@
       <c r="K4" s="2" t="n">
         <v>0.09</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>365</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -662,6 +794,34 @@
       <c r="K5" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>365</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIXED_ROW</t>
+          <t>FIXED_UNTOUCHED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,6 +852,29 @@
       </c>
       <c r="I6" s="2" t="n">
         <v>0.2999</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>365</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
   </sheetData>
